--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.20058</v>
+        <v>16.90327</v>
       </c>
       <c r="D2" t="n">
-        <v>16.4604</v>
+        <v>16.60523</v>
       </c>
       <c r="E2" t="n">
-        <v>16.61809</v>
+        <v>16.73815</v>
       </c>
       <c r="F2" t="n">
-        <v>42.86979</v>
+        <v>42.63821</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05137</v>
+        <v>0.05028</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84814</v>
+        <v>1.80837</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.73443</v>
+        <v>16.90517</v>
       </c>
       <c r="D3" t="n">
-        <v>16.71295</v>
+        <v>16.8518</v>
       </c>
       <c r="E3" t="n">
-        <v>17.00779</v>
+        <v>16.87303</v>
       </c>
       <c r="F3" t="n">
-        <v>42.76731</v>
+        <v>43.35091</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05103</v>
+        <v>0.0511</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81148</v>
+        <v>1.82139</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.85224</v>
+        <v>17.0985</v>
       </c>
       <c r="D4" t="n">
-        <v>16.49285</v>
+        <v>16.55674</v>
       </c>
       <c r="E4" t="n">
-        <v>16.57671</v>
+        <v>16.77645</v>
       </c>
       <c r="F4" t="n">
-        <v>42.69081</v>
+        <v>42.39206</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05154</v>
+        <v>0.05046</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83838</v>
+        <v>1.85276</v>
       </c>
     </row>
   </sheetData>
